--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO29"/>
+  <dimension ref="A1:AO30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="19">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="21">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4032,27 +4032,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="27">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="29">
@@ -4455,138 +4455,279 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO30"/>
+  <dimension ref="A1:AO32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="11">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="23">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="27">
@@ -4173,27 +4173,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="28">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,138 +4596,420 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>45890.89583333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="3" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AO30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="26">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="27">
@@ -4173,27 +4173,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="28">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.95833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4728,288 +4728,6 @@
         <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45890.89583333334</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Los Angeles II</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="3" t="n">
-        <v>45890.95833333334</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO30"/>
+  <dimension ref="A1:AO31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,138 +4596,279 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="3" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4361,7 +4361,7 @@
         <v>5.2</v>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4502,7 +4502,7 @@
         <v>5.2</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO31"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4737,138 +4737,702 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
+        <v>45890.79166666666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
+        <v>45890.89583333334</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>45890.89583333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="3" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4925,7 +4925,7 @@
         <v>5.2</v>
       </c>
       <c r="N32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5066,7 +5066,7 @@
         <v>5.2</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4925,7 +4925,7 @@
         <v>5.2</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5066,7 +5066,7 @@
         <v>5.2</v>
       </c>
       <c r="N33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M32" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="N32" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="M33" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N33" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N32" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AO37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>4.9</v>
+        <v>2.77</v>
       </c>
       <c r="N32" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="34">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5301,138 +5301,420 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3" t="n">
+        <v>45890.89583333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="3" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO37"/>
+  <dimension ref="A1:AO40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1776,27 +1776,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="17">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="24">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="27">
@@ -4173,27 +4173,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="28">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="29">
@@ -4455,27 +4455,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="30">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>2.77</v>
       </c>
       <c r="N35" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5583,138 +5583,561 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="3" t="n">
+        <v>45890.89583333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="3" t="n">
+        <v>45890.89583333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="3" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1494,27 +1494,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="10">
@@ -1776,27 +1776,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="11">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="M25" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="N25" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>2.23</v>
       </c>
       <c r="M26" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1.35</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.23</v>
+        <v>6.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.91</v>
+        <v>1.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="M27" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="N27" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>2.23</v>
       </c>
       <c r="M25" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.35</v>
+        <v>2.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.23</v>
+        <v>6.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>1.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="M24" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N25" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="N27" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3806,43 +3806,43 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3947,43 +3947,43 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>2.11</v>
       </c>
       <c r="M26" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="N26" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
         <v>1.35</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,83 +4214,83 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.11</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4928,31 +4928,31 @@
         <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X32" t="n">
         <v>2.18</v>
@@ -4961,16 +4961,16 @@
         <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>45890.79166666666</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO40"/>
+  <dimension ref="A1:AO30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="6">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="7">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="8">
@@ -1494,27 +1494,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="9">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="15">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3101,43 +3101,43 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3242,43 +3242,43 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3383,43 +3383,43 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3524,43 +3524,43 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3806,43 +3806,43 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="25">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3947,43 +3947,43 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -4032,27 +4032,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,98 +4073,98 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="M26" t="n">
-        <v>3.17</v>
+        <v>2.77</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="S26" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="V26" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="27">
@@ -4173,27 +4173,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.27</v>
+        <v>1.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.04</v>
+        <v>4.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.85</v>
+        <v>8.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="V27" t="n">
         <v>1.23</v>
       </c>
       <c r="W27" t="n">
-        <v>3.42</v>
+        <v>4.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.97</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.28</v>
+        <v>9</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="28">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="29">
@@ -4455,27 +4455,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.95833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4728,1416 +4728,6 @@
         <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Atlético PR</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AO32" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Paysandu</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Ferroviária</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Volta Redonda</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Universitario</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="3" t="n">
-        <v>45890.89583333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="3" t="n">
-        <v>45890.89583333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Los Angeles II</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="3" t="n">
-        <v>45890.95833333334</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3095,10 +3095,10 @@
         <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
         <v>1.35</v>
@@ -3137,7 +3137,7 @@
         <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.4</v>
+        <v>2.23</v>
       </c>
       <c r="M20" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>2.91</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="S20" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.8</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.03</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.25</v>
+        <v>2.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3377,10 +3377,10 @@
         <v>3.03</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
         <v>1.37</v>
@@ -3389,19 +3389,19 @@
         <v>2.84</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
         <v>1.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="V21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="X21" t="n">
         <v>1.9</v>
@@ -3413,10 +3413,10 @@
         <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
         <v>2.01</v>
@@ -3438,25 +3438,25 @@
         <v>1.55</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AI21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN21" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.23</v>
+        <v>6.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.91</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="R22" t="n">
-        <v>2.76</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.76</v>
+        <v>1.97</v>
       </c>
       <c r="T22" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>3.22</v>
+        <v>5.95</v>
       </c>
       <c r="X22" t="n">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.14</v>
+        <v>1.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,31 +3573,31 @@
         </is>
       </c>
       <c r="AF22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45890.625</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45890.625</v>
@@ -4652,25 +4652,25 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="X30" t="n">
         <v>1.88</v>
@@ -4679,16 +4679,16 @@
         <v>1.82</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO30"/>
+  <dimension ref="A1:AO26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1494,27 +1494,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,13 +2466,13 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO14" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,13 +2607,13 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45890.54166666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,83 +3227,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.23</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>2.91</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.85</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
         <v>1.4</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="AG20" t="n">
         <v>1.29</v>
       </c>
-      <c r="W20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN20" t="n">
         <v>1.85</v>
       </c>
-      <c r="AN20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AO20" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="21">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3468,27 +3468,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,98 +3509,98 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.4</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>5.3</v>
+        <v>2.77</v>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="P22" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="S22" t="n">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
         <v>1.8</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W22" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3609,27 +3609,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,52 +3650,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.68</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>3.71</v>
       </c>
       <c r="X23" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.63</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AB23" t="n">
         <v>2.25</v>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3750,27 +3750,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,83 +3791,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>8.4</v>
       </c>
       <c r="O24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2.6</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,13 +3876,13 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3891,27 +3891,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.66666666666</v>
+        <v>45890.95833333334</v>
       </c>
     </row>
     <row r="26">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>2.77</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>1.97</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.33</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,576 +4158,12 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.79166666666</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Universitario</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AO27" s="3" t="n">
-        <v>45890.89583333334</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AO28" s="3" t="n">
-        <v>45890.89583333334</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Los Angeles II</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="n">
-        <v>45890.95833333334</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -789,7 +789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,40 +2381,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="O14" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.84</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="X14" t="n">
         <v>1.9</v>
@@ -2423,16 +2423,16 @@
         <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="n">
         <v>2.9</v>
@@ -2457,7 +2457,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.23</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.91</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.85</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AI15" t="n">
         <v>2.8</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2678,10 +2678,10 @@
         <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>2.65</v>
@@ -2693,10 +2693,10 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="X16" t="n">
         <v>1.83</v>
@@ -2708,13 +2708,13 @@
         <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
         <v>2.97</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="P17" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.8</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W17" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y17" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>3</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.25</v>
+        <v>2.96</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.625</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,95 +3227,95 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.25</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AC20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
         <v>3.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.44</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3717,16 +3717,16 @@
         <v>1.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AH23" t="n">
         <v>1.73</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
         <v>3.75</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
         <v>3.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="X24" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
         <v>1.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AH24" t="n">
         <v>1.73</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN24" t="n">
         <v>3.75</v>
@@ -4100,10 +4100,10 @@
         <v>1.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
         <v>3.4</v>
@@ -4115,10 +4115,10 @@
         <v>1.82</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB26" t="n">
         <v>1.73</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
@@ -4146,10 +4146,10 @@
         <v>4.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -794,22 +794,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="N14" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>1.85</v>
@@ -2399,13 +2399,13 @@
         <v>1.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="S14" t="n">
         <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="U14" t="n">
         <v>1.06</v>
@@ -2417,13 +2417,13 @@
         <v>3.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
         <v>1.25</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
         <v>2.9</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AJ14" t="n">
         <v>3.6</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,83 +2663,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,34 +2804,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="U17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>1.29</v>
@@ -2840,22 +2840,22 @@
         <v>3.4</v>
       </c>
       <c r="X17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>1.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.625</v>
@@ -3101,19 +3101,19 @@
         <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.55</v>
@@ -3131,7 +3131,7 @@
         <v>5.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AB19" t="n">
         <v>2.2</v>
@@ -3162,7 +3162,7 @@
         <v>1.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4100,25 +4100,25 @@
         <v>1.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X26" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB26" t="n">
         <v>1.73</v>
@@ -4149,7 +4149,7 @@
         <v>2.15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -789,27 +789,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="O14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
         <v>1.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.3</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.1</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W15" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AI15" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.75</v>
+        <v>3.32</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,83 +2663,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O16" t="n">
         <v>3.1</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.93</v>
-      </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="R16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI16" t="n">
         <v>2.8</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.95</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>1.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.625</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,95 +3086,95 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.2</v>
       </c>
       <c r="U19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.11</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.55</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -789,12 +789,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.32</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O14" t="n">
         <v>3.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.93</v>
-      </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="R14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AI14" t="n">
         <v>2.8</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>5.46</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.26</v>
+        <v>2.89</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.8</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3</v>
-      </c>
       <c r="Z16" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.09</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
         <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,95 +3227,95 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.11</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.55</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
         <v>3.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="X23" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3717,16 +3717,16 @@
         <v>1.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AH23" t="n">
         <v>1.73</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
         <v>3.75</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
         <v>3.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA24" t="n">
         <v>1.44</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
         <v>1.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AH24" t="n">
         <v>1.73</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
         <v>3.75</v>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="M26" t="n">
         <v>3.3</v>
@@ -4094,7 +4094,7 @@
         <v>2.88</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="T26" t="n">
         <v>1.4</v>
@@ -4103,16 +4103,16 @@
         <v>1.03</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="X26" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Z26" t="n">
         <v>3.2</v>
@@ -4137,16 +4137,16 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
         <v>2.56</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>2.29</v>
       </c>
       <c r="M14" t="n">
-        <v>5.46</v>
+        <v>3.29</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="P14" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="R14" t="n">
-        <v>4.33</v>
+        <v>2.91</v>
       </c>
       <c r="S14" t="n">
-        <v>1.97</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.04</v>
+        <v>5.46</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="O15" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="R15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y15" t="n">
         <v>3</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.97</v>
+        <v>5.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.29</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="O17" t="n">
+      <c r="S17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.85</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>1.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,95 +3086,95 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.2</v>
       </c>
       <c r="U19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.11</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.55</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>3.09</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -789,12 +789,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="O14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="U14" t="n">
         <v>1.06</v>
       </c>
       <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.3</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2448,16 +2448,16 @@
         <v>1.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>5.46</v>
+        <v>3.04</v>
       </c>
       <c r="N15" t="n">
-        <v>1.26</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="P15" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="R15" t="n">
-        <v>4.33</v>
+        <v>2.89</v>
       </c>
       <c r="S15" t="n">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="X15" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.75</v>
+        <v>2.93</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2666,55 +2666,55 @@
         <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.38</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>5.46</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="R17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y17" t="n">
         <v>3</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.97</v>
+        <v>5.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.625</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,95 +3227,95 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.11</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.55</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
         <v>1.93</v>
@@ -2417,7 +2417,7 @@
         <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Y14" t="n">
         <v>1.8</v>
@@ -2558,10 +2558,10 @@
         <v>3.4</v>
       </c>
       <c r="X15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,84 +2663,84 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>6.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="R16" t="n">
-        <v>2.72</v>
+        <v>4.33</v>
       </c>
       <c r="S16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI16" t="n">
         <v>2.8</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AJ16" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>2.23</v>
       </c>
       <c r="M17" t="n">
-        <v>5.46</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>2.91</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="S17" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.8</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>1.36</v>
       </c>
-      <c r="Y17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.625</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3233,7 +3233,7 @@
         <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>2.1</v>
@@ -3242,10 +3242,10 @@
         <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S20" t="n">
         <v>4.2</v>
@@ -3254,31 +3254,31 @@
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="Y20" t="n">
         <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
         <v>1.11</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.28</v>
+        <v>4.1</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>4.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Z24" t="n">
         <v>2.76</v>
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4094,13 +4094,13 @@
         <v>2.88</v>
       </c>
       <c r="S26" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
         <v>1.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="V26" t="n">
         <v>1.25</v>
@@ -4109,10 +4109,10 @@
         <v>3.28</v>
       </c>
       <c r="X26" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Z26" t="n">
         <v>3.2</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
@@ -4149,7 +4149,7 @@
         <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO26"/>
+  <dimension ref="A1:AO27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -789,7 +789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>6.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>5.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>1.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="R14" t="n">
-        <v>2.84</v>
+        <v>4.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>1.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,55 +2522,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="O15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X15" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>2.05</v>
@@ -2589,16 +2589,16 @@
         <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.4</v>
+        <v>2.23</v>
       </c>
       <c r="M16" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="S16" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,84 +2804,84 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R17" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="U17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.33</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AB17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3.2</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,59 +3509,59 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="M22" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="O22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.44</v>
       </c>
-      <c r="R22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45890.79166666666</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,98 +3650,98 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>2.22</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>2.77</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.33</v>
       </c>
-      <c r="P23" t="n">
+      <c r="U23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN23" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AO23" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,13 +4017,13 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="26">
@@ -4032,138 +4032,279 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>3.5</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>3.45</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>1.97</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1.36</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>2.88</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>2.7</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>1.4</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>1.02</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V27" t="n">
         <v>1.25</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>3.28</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>1.88</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y27" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z27" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA27" t="n">
         <v>1.28</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AB27" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AC27" t="n">
         <v>2</v>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
         <v>1.24</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AH27" t="n">
         <v>4.13</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AI27" t="n">
         <v>2.12</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AJ27" t="n">
         <v>2.5</v>
       </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="3" t="n">
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.4</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>1.35</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>4.33</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.83</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="n">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,55 +2522,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R15" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X15" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
         <v>2.05</v>
@@ -2589,28 +2589,28 @@
         <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="AI15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN15" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.15</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="R17" t="n">
-        <v>2.89</v>
+        <v>4.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="U17" t="n">
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.93</v>
+        <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,95 +3086,95 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="S19" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>4.67</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="N22" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AI22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45890.79166666666</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,59 +3650,59 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="O23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.44</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.38</v>
-      </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="X23" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45890.79166666666</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AO26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -789,12 +789,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -930,7 +930,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,13 +2466,13 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,55 +2522,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="O15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X15" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>2.05</v>
@@ -2589,16 +2589,16 @@
         <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,84 +2663,84 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R16" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.33</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AB16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>3.2</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>2.23</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.91</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="S17" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="T19" t="n">
         <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>4.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,95 +3227,95 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="S20" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,83 +3650,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.74</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AG23" t="n">
         <v>3.3</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="AH23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.5</v>
       </c>
-      <c r="X23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>4.33</v>
+        <v>9.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,13 +4017,13 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.95833333334</v>
       </c>
     </row>
     <row r="26">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4088,43 +4088,43 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4164,147 +4164,6 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45890.95833333334</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -789,7 +789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1706,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>5.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.03</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.36</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>1.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.96</v>
+        <v>6.41</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T16" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2730,16 +2730,16 @@
         <v>1.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,40 +2804,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
         <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="X17" t="n">
         <v>1.9</v>
@@ -2846,16 +2846,16 @@
         <v>1.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,83 +2945,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="R18" t="n">
-        <v>4.33</v>
+        <v>2.93</v>
       </c>
       <c r="S18" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="U18" t="n">
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>6</v>
+        <v>3.64</v>
       </c>
       <c r="X18" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AI18" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,95 +3086,95 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U19" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
         <v>3.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.44</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3717,16 +3717,16 @@
         <v>1.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AH23" t="n">
         <v>1.73</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
         <v>3.75</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
         <v>3.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="X24" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
         <v>1.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AH24" t="n">
         <v>1.73</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN24" t="n">
         <v>3.75</v>
@@ -4094,10 +4094,10 @@
         <v>2.88</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U26" t="n">
         <v>1.02</v>
@@ -4149,7 +4149,7 @@
         <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -794,22 +794,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>3.79</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1409,43 +1409,43 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,58 +1535,58 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.25</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="N9" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1826,49 +1826,49 @@
         <v>1.82</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,59 +2099,59 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.5</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.5</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AC12" t="n">
         <v>2.4</v>
       </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>1.46</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
@@ -2540,34 +2540,34 @@
         <v>1.18</v>
       </c>
       <c r="R15" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="S15" t="n">
         <v>1.91</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
         <v>6.5</v>
       </c>
       <c r="X15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Y15" t="n">
         <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
         <v>1.6</v>
@@ -2592,13 +2592,13 @@
         <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.41</v>
+        <v>6</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.33</v>
       </c>
-      <c r="W16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,31 +2727,31 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AI16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN16" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
         <v>1.93</v>
@@ -2819,10 +2819,10 @@
         <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
         <v>2.7</v>
@@ -2831,22 +2831,22 @@
         <v>1.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="V17" t="n">
         <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
         <v>1.3</v>
@@ -2855,7 +2855,7 @@
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
         <v>1.53</v>
@@ -2877,10 +2877,10 @@
         <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U18" t="n">
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3012,16 +3012,16 @@
         <v>1.33</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH18" t="n">
         <v>2.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="X19" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.6</v>
+        <v>4.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45890.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,95 +3227,95 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.25</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AC20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.85</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45890.625</v>
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4091,13 +4091,13 @@
         <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U26" t="n">
         <v>1.02</v>
@@ -4109,10 +4109,10 @@
         <v>3.28</v>
       </c>
       <c r="X26" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Z26" t="n">
         <v>3.2</v>
@@ -4140,16 +4140,16 @@
         <v>1.24</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="AI26" t="n">
         <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -648,27 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -789,27 +789,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>3.68</v>
+        <v>1.46</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
         <v>1.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>1.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.63</v>
+        <v>8.75</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,84 +1535,84 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.62</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,83 +1676,83 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.3</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="AA9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
         <v>1.25</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,95 +1817,95 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>3.13</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="U10" t="n">
         <v>1.09</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="X10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="AN10" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.67</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,83 +1958,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="M11" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="S11" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
         <v>1.6</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="S12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X12" t="n">
         <v>2.25</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,16 +2163,16 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
         <v>4.33</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,83 +2240,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="N13" t="n">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.3</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
         <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
         <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>4.3</v>
+        <v>1.95</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.91</v>
+        <v>2.84</v>
       </c>
       <c r="T15" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.32</v>
+        <v>1.99</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="AH15" t="n">
-        <v>6</v>
+        <v>2.93</v>
       </c>
       <c r="AI15" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,95 +2663,95 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="T16" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>3.42</v>
+        <v>6.5</v>
       </c>
       <c r="X16" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.1</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
         <v>2.75</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
         <v>1.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="X18" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
         <v>3.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="X23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3717,16 +3717,16 @@
         <v>1.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AH23" t="n">
         <v>1.73</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
         <v>3.75</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
         <v>3.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA24" t="n">
         <v>1.44</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
         <v>1.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AH24" t="n">
         <v>1.73</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
         <v>3.75</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.4</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>3.68</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="U7" t="n">
         <v>1.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="n">
-        <v>8.75</v>
+        <v>2.63</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>4.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>1.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>3.74</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="V9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.15</v>
       </c>
-      <c r="W9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1743,16 +1743,16 @@
         <v>1.25</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AI9" t="n">
         <v>2</v>
       </c>
-      <c r="AH9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.53</v>
+        <v>4.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.46</v>
+        <v>1.37</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
         <v>1.09</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="M11" t="n">
         <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
         <v>2.3</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>3.13</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="R12" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="X12" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.63</v>
+        <v>4.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,83 +2240,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.3</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AA13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
         <v>1.25</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.33</v>
       </c>
-      <c r="W15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="n">
         <v>2.93</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.6</v>
+        <v>3.43</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,83 +2663,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.3</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH16" t="n">
         <v>3</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>6</v>
-      </c>
       <c r="AI16" t="n">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,95 +2804,95 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="U17" t="n">
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>3.42</v>
+        <v>6.5</v>
       </c>
       <c r="X17" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R18" t="n">
         <v>2.75</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
         <v>1.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Z18" t="n">
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45890.60416666666</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO26"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,130 +513,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>homeGoals</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>awayGoals</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_HT1</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT1</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT1</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_H</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_A</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -648,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -728,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,18 +722,18 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD2" t="n">
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -762,25 +742,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>4.5</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -789,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -883,18 +851,18 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD3" t="n">
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -908,20 +876,8 @@
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="3" t="n">
-        <v>45890.41666666666</v>
+      <c r="AK3" s="3" t="n">
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -930,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,19 +927,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1007,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1024,45 +980,33 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD4" t="n">
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1076,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1165,18 +1109,18 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD5" t="n">
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1190,19 +1134,7 @@
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="3" t="n">
+      <c r="AK5" s="3" t="n">
         <v>45890.5</v>
       </c>
     </row>
@@ -1217,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1306,18 +1238,18 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD6" t="n">
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1331,19 +1263,7 @@
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45890.5</v>
       </c>
     </row>
@@ -1358,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,97 +1314,85 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.17</v>
+        <v>5.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.65</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="n">
-        <v>1.22</v>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -1499,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,97 +1443,85 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>1.82</v>
+        <v>3.68</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.57</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2.25</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.15</v>
+        <v>4.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="n">
-        <v>1.35</v>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG8" t="n">
         <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -1676,97 +1572,85 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI9" t="n">
         <v>4.3</v>
       </c>
-      <c r="P9" t="n">
+      <c r="AJ9" t="n">
         <v>1.37</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO9" s="3" t="n">
+      <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -1791,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,97 +1701,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO10" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -1967,88 +1839,76 @@
         <v>2.12</v>
       </c>
       <c r="O11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.3</v>
       </c>
-      <c r="P11" t="n">
+      <c r="AJ11" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO11" s="3" t="n">
+      <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -2099,97 +1959,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="O12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.5</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AJ12" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO12" s="3" t="n">
+      <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -2249,88 +2097,76 @@
         <v>3.95</v>
       </c>
       <c r="O13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.53</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Z13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.46</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AO13" s="3" t="n">
+      <c r="AK13" s="3" t="n">
         <v>45890.52083333334</v>
       </c>
     </row>
@@ -2434,18 +2270,18 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD14" t="n">
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2459,19 +2295,7 @@
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45890.58333333334</v>
       </c>
     </row>
@@ -2531,88 +2355,76 @@
         <v>2.85</v>
       </c>
       <c r="O15" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.95</v>
       </c>
-      <c r="P15" t="n">
+      <c r="AJ15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO15" s="3" t="n">
+      <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
       </c>
     </row>
@@ -2672,88 +2484,76 @@
         <v>2.92</v>
       </c>
       <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.93</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AJ16" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO16" s="3" t="n">
+      <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
       </c>
     </row>
@@ -2813,88 +2613,76 @@
         <v>1.3</v>
       </c>
       <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI17" t="n">
         <v>3.1</v>
       </c>
-      <c r="P17" t="n">
+      <c r="AJ17" t="n">
         <v>1.35</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO17" s="3" t="n">
+      <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
       </c>
     </row>
@@ -2954,88 +2742,76 @@
         <v>2.95</v>
       </c>
       <c r="O18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.85</v>
       </c>
-      <c r="P18" t="n">
+      <c r="AJ18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO18" s="3" t="n">
+      <c r="AK18" s="3" t="n">
         <v>45890.60416666666</v>
       </c>
     </row>
@@ -3060,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,97 +2862,85 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>3.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>2.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.54</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="n">
-        <v>1.33</v>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO19" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45890.625</v>
       </c>
     </row>
@@ -3201,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,97 +2991,85 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>4.67</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>2.29</v>
       </c>
       <c r="T20" t="n">
-        <v>1.23</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>1.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="n">
-        <v>1.44</v>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO20" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45890.625</v>
       </c>
     </row>
@@ -3421,18 +3173,18 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD21" t="n">
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF21" t="n">
-        <v>0</v>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3446,19 +3198,7 @@
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="3" t="n">
+      <c r="AK21" s="3" t="n">
         <v>45890.66666666666</v>
       </c>
     </row>
@@ -3518,88 +3258,76 @@
         <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.44</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>2.63</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>3.25</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>1.33</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>1.07</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>1.38</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>3</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>2.18</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>3.9</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD22" t="n">
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF22" t="n">
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AH22" t="n">
-        <v>3</v>
-      </c>
       <c r="AI22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN22" t="n">
         <v>2.25</v>
       </c>
-      <c r="AO22" s="3" t="n">
+      <c r="AK22" s="3" t="n">
         <v>45890.79166666666</v>
       </c>
     </row>
@@ -3659,88 +3387,76 @@
         <v>9.6</v>
       </c>
       <c r="O23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.33</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AO23" s="3" t="n">
+      <c r="AK23" s="3" t="n">
         <v>45890.89583333334</v>
       </c>
     </row>
@@ -3800,88 +3516,76 @@
         <v>8.4</v>
       </c>
       <c r="O24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.3</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W24" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AO24" s="3" t="n">
+      <c r="AK24" s="3" t="n">
         <v>45890.89583333334</v>
       </c>
     </row>
@@ -3985,18 +3689,18 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD25" t="n">
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF25" t="n">
-        <v>0</v>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -4010,19 +3714,7 @@
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="3" t="n">
+      <c r="AK25" s="3" t="n">
         <v>45890.95833333334</v>
       </c>
     </row>
@@ -4082,88 +3774,76 @@
         <v>1.93</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.36</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>2.8</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>2.62</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>1.38</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>1.02</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>1.25</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>3.28</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>1.86</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>1.28</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>2</v>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF26" t="n">
-        <v>1.24</v>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG26" t="n">
         <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2.25</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.56</v>
-      </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
         <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>5.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.27</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
         <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>3.88</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.74</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.35</v>
+        <v>2.41</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>3.27</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.29</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AI13" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="M15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="O15" t="n">
         <v>2.93</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
         <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>6.4</v>
       </c>
       <c r="M16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI16" t="n">
         <v>3.1</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>5.4</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.3</v>
       </c>
-      <c r="O17" t="n">
-        <v>6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="AC17" t="n">
         <v>1.7</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.33</v>
       </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O24" t="n">
         <v>1.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,10 +3577,10 @@
         <v>1.05</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ24" t="n">
         <v>3.75</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1185,49 +1185,49 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.68</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>2.63</v>
+        <v>7.5</v>
       </c>
       <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1384,13 +1384,13 @@
         <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1452,19 +1452,19 @@
         <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
         <v>3.6</v>
@@ -1485,10 +1485,10 @@
         <v>2.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AB8" t="n">
         <v>1.09</v>
@@ -1497,7 +1497,7 @@
         <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
         <v>1.57</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="O9" t="n">
-        <v>8.75</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,62 +1701,62 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X10" t="n">
         <v>4.6</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
         <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
         <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.75</v>
+        <v>5.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,62 +1959,62 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.73</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.27</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
         <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Y13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45890.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.4</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>5.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
         <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>1.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>1.87</v>
       </c>
-      <c r="AA18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
         <v>3.8</v>
@@ -2886,16 +2886,16 @@
         <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
         <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
         <v>2.1</v>
@@ -2904,19 +2904,19 @@
         <v>3.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AA19" t="n">
         <v>6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI19" t="n">
         <v>2.1</v>
@@ -3000,19 +3000,19 @@
         <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
         <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T20" t="n">
         <v>3.6</v>
@@ -3021,13 +3021,13 @@
         <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
         <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
         <v>2.5</v>
@@ -3036,10 +3036,10 @@
         <v>1.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
         <v>2.2</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
         <v>1.25</v>
@@ -3120,34 +3120,34 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45890.66666666666</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.73</v>
       </c>
       <c r="P24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.44</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,10 +3577,10 @@
         <v>1.05</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ24" t="n">
         <v>3.75</v>
@@ -3765,58 +3765,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O26" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
         <v>2</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2.25</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.54</v>
-      </c>
       <c r="Z7" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.37</v>
+        <v>2.55</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="P9" t="n">
         <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,62 +1701,62 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.25</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.41</v>
+        <v>1.45</v>
       </c>
       <c r="AA10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>3.99</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
@@ -1983,37 +1983,37 @@
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
         <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Z12" t="n">
         <v>1.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.57</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA14" t="n">
         <v>4.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>1.4</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA15" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AD15" t="n">
         <v>2</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.17</v>
+        <v>3.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>1.97</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>1.87</v>
       </c>
-      <c r="AA17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.35</v>
       </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AB18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.67</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AA19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="S20" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45890.625</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
         <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
         <v>1.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI21" t="n">
         <v>1.44</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>3.99</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
         <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
         <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2.25</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.56</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,13 +1513,13 @@
         <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>1.73</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>7.5</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AI9" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.1</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.25</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="R10" t="n">
         <v>1.57</v>
@@ -1734,50 +1734,50 @@
         <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.45</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.88</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.1</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3.99</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,13 +2029,13 @@
         <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,62 +2088,62 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>3.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>2.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.41</v>
+        <v>1.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>5.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
@@ -2355,49 +2355,49 @@
         <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.17</v>
+        <v>3.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.8</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AD15" t="n">
         <v>2</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.75</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.77</v>
-      </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.67</v>
+        <v>3.17</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>6.5</v>
+        <v>3.47</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O24" t="n">
         <v>1.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,10 +3577,10 @@
         <v>1.05</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ24" t="n">
         <v>3.75</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1194,28 +1194,28 @@
         <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>1.5</v>
@@ -1230,13 +1230,13 @@
         <v>1.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD6" t="n">
         <v>1.62</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" t="n">
         <v>1.8</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.19</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.99</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>4.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>2.6</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.67</v>
+        <v>4.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.55</v>
+        <v>1.37</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,62 +1572,62 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.25</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.41</v>
+        <v>1.45</v>
       </c>
       <c r="AA9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>2.13</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
         <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>5.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.5</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AI11" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.55</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.62</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>6.81</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
         <v>2.02</v>
@@ -2256,10 +2256,10 @@
         <v>2.65</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
         <v>4.1</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,25 +2346,25 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.59</v>
+        <v>3.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
         <v>2.75</v>
@@ -2373,22 +2373,22 @@
         <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
         <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
         <v>3.3</v>
@@ -2397,10 +2397,10 @@
         <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>5.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.8</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
         <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.4</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.35</v>
       </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AB18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.67</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
         <v>4.5</v>
@@ -2883,22 +2883,22 @@
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V19" t="n">
         <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Y19" t="n">
         <v>2.5</v>
@@ -2907,16 +2907,16 @@
         <v>1.38</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AB19" t="n">
         <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="n">
         <v>1.25</v>
@@ -2991,55 +2991,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
         <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S20" t="n">
         <v>2.1</v>
       </c>
       <c r="T20" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
         <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AA20" t="n">
         <v>6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
         <v>2.13</v>
@@ -3765,58 +3765,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="N26" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
         <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AD26" t="n">
         <v>2</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="Z6" t="n">
         <v>1.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.12</v>
+        <v>5.13</v>
       </c>
       <c r="AB6" t="n">
         <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AI6" t="n">
         <v>1.8</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>3.23</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.22</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>3.66</v>
       </c>
       <c r="O8" t="n">
-        <v>9.4</v>
+        <v>2.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.37</v>
+        <v>2.55</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>1.73</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.51</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.25</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1710,10 +1710,10 @@
         <v>2.13</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
@@ -1731,7 +1731,7 @@
         <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
         <v>1.55</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
         <v>2.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>6.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.41</v>
+        <v>1.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.53</v>
+        <v>4.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.46</v>
+        <v>1.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.7</v>
+        <v>2.53</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.2</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.18</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
         <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>2.64</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,86 +2217,86 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>2.39</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.050000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AK14" s="3" t="n">
-        <v>45890.58333333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.47</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.17</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.4</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.35</v>
       </c>
-      <c r="O16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S16" t="n">
-        <v>4.5</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.95</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
         <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
         <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AA17" t="n">
         <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="n">
         <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,86 +2733,86 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="Y18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AK18" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="S19" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="U19" t="n">
         <v>1.2</v>
       </c>
       <c r="V19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.11</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,86 +2991,86 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.64</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
         <v>2.62</v>
       </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="Y20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>3.4</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AK20" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>2.77</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
         <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45890.66666666666</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,86 +3249,86 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.77</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="AD22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>3.75</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AK22" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.95833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,135 +3715,6 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45890.95833333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,62 +927,62 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.75</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.8</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.23</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>3.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.66</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.1</v>
+        <v>5.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,62 +1572,62 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X9" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="Y9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.57</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>3.66</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>2.58</v>
       </c>
       <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.37</v>
+        <v>2.55</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="T12" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
         <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>2.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.15</v>
+        <v>8.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="T13" t="n">
         <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
         <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AI13" t="n">
         <v>1.4</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="M14" t="n">
         <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AB14" t="n">
         <v>1.33</v>
       </c>
-      <c r="X14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,13 +2287,13 @@
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.4</v>
+        <v>2.39</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.97</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA16" t="n">
         <v>3.3</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.47</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.17</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI17" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="S18" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="V18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.11</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.625</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y19" t="n">
         <v>2.6</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>3.08</v>
-      </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -2991,19 +2991,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
         <v>6.75</v>
@@ -3018,10 +3018,10 @@
         <v>3.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
         <v>1.42</v>
@@ -3039,7 +3039,7 @@
         <v>4.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
         <v>2.35</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AI20" t="n">
         <v>1.44</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         <v>1.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ22" t="n">
         <v>3.75</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.8</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45890.5</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Z5" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.13</v>
+        <v>3.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
         <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,62 +1443,62 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="T8" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
         <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="Z8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.38</v>
       </c>
-      <c r="AA8" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.5</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AJ10" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>2.74</v>
+        <v>4.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>2.41</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.5</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA14" t="n">
         <v>3.3</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
         <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.39</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P15" t="n">
         <v>3</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.17</v>
       </c>
       <c r="R16" t="n">
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
         <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>5.8</v>
+        <v>3.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.97</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.95</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3516,52 +3516,52 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,86 +927,86 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X4" t="n">
         <v>3.6</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.25</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1056,43 +1056,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
         <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="T5" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Y5" t="n">
         <v>2.1</v>
@@ -1101,16 +1101,16 @@
         <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" t="n">
         <v>1.62</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>2.74</v>
+        <v>4.71</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>3.23</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>4.04</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.1</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.55</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1722,13 +1722,13 @@
         <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
         <v>3.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
         <v>1.09</v>
@@ -1755,7 +1755,7 @@
         <v>2.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
         <v>1.24</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="P11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.74</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>2.56</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.97</v>
+        <v>1.51</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>6.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.45</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.71</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AH13" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45890.58333333334</v>
+        <v>45890.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.91</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.4</v>
+        <v>2.23</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>2.91</v>
       </c>
       <c r="O15" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>3.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>3.14</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>3.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2487,31 +2487,31 @@
         <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
         <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
         <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
         <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="Y16" t="n">
         <v>1.83</v>
@@ -2520,10 +2520,10 @@
         <v>1.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
         <v>1.67</v>
@@ -2545,7 +2545,7 @@
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
         <v>1.95</v>
@@ -2613,34 +2613,34 @@
         <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>3.17</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
         <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
         <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y17" t="n">
         <v>1.9</v>
@@ -2652,7 +2652,7 @@
         <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
         <v>1.72</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,86 +2733,86 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>2.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.72</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>4.25</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.15</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S19" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
         <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.45</v>
       </c>
-      <c r="AA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="N20" t="n">
-        <v>5.75</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>2.21</v>
+        <v>5.12</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.75</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45890.66666666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,86 +3120,86 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>2.77</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>7.13</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
         <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,86 +3249,86 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>2.77</v>
       </c>
       <c r="N22" t="n">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.5</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>3.71</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.04</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AK22" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,86 +3507,86 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="P24" t="n">
         <v>2.5</v>
       </c>
       <c r="Q24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>3.75</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3" t="n">
-        <v>45890.95833333334</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,126 +3595,255 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45890.95833333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M26" t="n">
         <v>3.45</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="N26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.35</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>2.85</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="T26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.02</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="W26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2</v>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="M8" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.04</v>
+        <v>3.78</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI8" t="n">
         <v>2.5</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AJ8" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.66</v>
+        <v>1.89</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>4.74</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.1</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.88</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.72</v>
+        <v>1.92</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.55</v>
+        <v>3.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,62 +1830,62 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
       <c r="O11" t="n">
-        <v>3.08</v>
+        <v>13.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.22</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.25</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.95</v>
+        <v>4.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.38</v>
+        <v>1.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.5</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>4.04</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.4</v>
+        <v>4.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,86 +2088,86 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>6.17</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.51</v>
+        <v>6.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.25</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45890.52083333334</v>
+        <v>45890.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,86 +2217,86 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>2.27</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.1</v>
       </c>
-      <c r="P14" t="n">
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AK14" s="3" t="n">
-        <v>45890.58333333334</v>
+        <v>45890.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>5.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>3.42</v>
+        <v>6.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>1.87</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,86 +2733,86 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="M18" t="n">
-        <v>5.3</v>
+        <v>2.82</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
-        <v>5.8</v>
+        <v>5.12</v>
       </c>
       <c r="P18" t="n">
-        <v>2.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.18</v>
       </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AI18" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45890.60416666666</v>
+        <v>45890.625</v>
       </c>
     </row>
     <row r="19">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,86 +2991,86 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>1.63</v>
       </c>
       <c r="M20" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>5.12</v>
+        <v>2.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.7</v>
+        <v>7.13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
         <v>1.15</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.24</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI20" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45890.625</v>
+        <v>45890.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>2.77</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.13</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
         <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45890.66666666666</v>
+        <v>45890.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,86 +3249,86 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.77</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="AD22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>3.75</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AK22" s="3" t="n">
-        <v>45890.79166666666</v>
+        <v>45890.89583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.73</v>
+        <v>2.34</v>
       </c>
       <c r="P24" t="n">
         <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.5</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>3.71</v>
+        <v>5.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>1.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>2.93</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45890.89583333334</v>
+        <v>45890.95833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O25" t="n">
-        <v>2.34</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>5.75</v>
+        <v>3.34</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>2.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,135 +3715,6 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45890.95833333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45890.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="X7" t="n">
-        <v>4.71</v>
+        <v>2.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.43</v>
+        <v>7.9</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="O8" t="n">
-        <v>3.78</v>
+        <v>13.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
         <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
         <v>2.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AB8" t="n">
         <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>4.74</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.47</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>4.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.66</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>4.74</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>3.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N11" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>13.1</v>
+        <v>4.04</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>4.25</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>4.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="M12" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4.04</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.5</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AJ12" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.75</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.89</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH14" t="n">
         <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>5.8</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>6.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>2.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>5.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.17</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O5" t="n">
         <v>3.2</v>
       </c>
-      <c r="N5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.28</v>
-      </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.05</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.61</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>3.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>3.66</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>3.69</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
         <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="O8" t="n">
-        <v>13.1</v>
+        <v>4.74</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
         <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>5.27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X9" t="n">
-        <v>4.71</v>
+        <v>3.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="O10" t="n">
-        <v>4.74</v>
+        <v>3.78</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
         <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>4.04</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>4.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.17</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AH11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.43</v>
+        <v>6.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.78</v>
+        <v>13.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AB12" t="n">
         <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>6.17</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
         <v>2.15</v>
@@ -2127,7 +2127,7 @@
         <v>2.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
         <v>1.55</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="O14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
         <v>2.8</v>
@@ -2250,10 +2250,10 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.9</v>
@@ -2265,10 +2265,10 @@
         <v>3.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
         <v>1.95</v>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,43 +2346,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X15" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
         <v>1.9</v>
@@ -2391,16 +2391,16 @@
         <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>5.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>3.42</v>
+        <v>6.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>1.87</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.99</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99</v>
+        <v>1.87</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.32</v>
       </c>
       <c r="AC17" t="n">
         <v>1.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="M18" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="N18" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="O18" t="n">
-        <v>5.12</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" t="n">
         <v>2.6</v>
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N19" t="n">
         <v>2.8</v>
       </c>
-      <c r="M19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3</v>
-      </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
         <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="U19" t="n">
         <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AI19" t="n">
         <v>2.1</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O20" t="n">
         <v>2.23</v>
@@ -3030,10 +3030,10 @@
         <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
         <v>4.2</v>
@@ -3645,16 +3645,16 @@
         <v>1.97</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
         <v>2.85</v>
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
         <v>1.88</v>
@@ -3681,16 +3681,16 @@
         <v>1.82</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
         <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -665,65 +665,65 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -794,65 +794,65 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,106 +886,106 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '63', '71']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.5</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="M5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.9</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Y5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.6</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="AB5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.23</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.69</v>
+        <v>13.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.15</v>
+        <v>6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.82</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
-        <v>4.74</v>
+        <v>2.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.47</v>
+        <v>5.27</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.55</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>3.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.66</v>
+        <v>2.13</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>3.78</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.27</v>
+        <v>2.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.29</v>
       </c>
-      <c r="X9" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,62 +1701,62 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.78</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.99</v>
+        <v>4.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>2.14</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.18</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="X10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.3</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.24</v>
+        <v>1.59</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>13.1</v>
+        <v>4.74</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
         <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.4</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.32</v>
       </c>
       <c r="AC17" t="n">
         <v>1.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -3516,22 +3516,22 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
         <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>1.76</v>
@@ -3540,28 +3540,28 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,87 +1052,87 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.97</v>
+        <v>2.37</v>
       </c>
       <c r="M5" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="N5" t="n">
-        <v>3.69</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.4</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1149,26 +1149,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1181,87 +1181,87 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="M6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.9</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Y6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3.6</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="AB6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,62 +1314,62 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>2.08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>13.1</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.82</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="N8" t="n">
-        <v>4.33</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>2.29</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.27</v>
+        <v>2.33</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.13</v>
+        <v>4.33</v>
       </c>
       <c r="O9" t="n">
-        <v>3.78</v>
+        <v>2.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.99</v>
+        <v>5.27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['11', '84', '89']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.18</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,87 +1697,87 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="O10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.46</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="T10" t="n">
-        <v>2.31</v>
+        <v>4.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.46</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1826,69 +1826,69 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.14</v>
+        <v>3.96</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.3</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AA11" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82', '90+10']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1933,87 +1933,87 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
-        <v>4.74</v>
+        <v>9.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AA12" t="n">
         <v>5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '26', '45+4', '48']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2241,38 +2241,38 @@
         <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
         <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.57</v>
       </c>
       <c r="M15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.04</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.8</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
         <v>1.95</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.03</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2607,31 +2607,31 @@
         <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -2640,25 +2640,25 @@
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>6.5</v>
+        <v>6.69</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" t="n">
         <v>3.1</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.95</v>
+        <v>2.67</v>
       </c>
       <c r="M18" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="T18" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.44</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.625</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="M19" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.51</v>
+        <v>4.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         <v>1.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ22" t="n">
         <v>3.75</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -1020,26 +1020,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.37</v>
+        <v>1.97</v>
       </c>
       <c r="M5" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48</v>
+        <v>3.69</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.62</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1149,26 +1149,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.97</v>
+        <v>2.37</v>
       </c>
       <c r="M6" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="N6" t="n">
-        <v>3.69</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.4</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,87 +1310,87 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.08</v>
+        <v>5.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="N7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>2.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.33</v>
+        <v>5.27</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '84', '89']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['11', '84', '89']</t>
+          <t>['82', '90+10']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>1.31</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>9.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="S10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="T10" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.13</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1764,20 +1764,20 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '26', '45+4', '48']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.96</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>2.11</v>
       </c>
       <c r="T11" t="n">
-        <v>2.29</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.66</v>
       </c>
       <c r="X11" t="n">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.34</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['82', '90+10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,87 +1933,87 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="O12" t="n">
-        <v>9.25</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
         <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>2.09</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['23', '26', '45+4', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2084,81 +2084,81 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.81</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60', '65']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" t="n">
         <v>1.4</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81', '89']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA15" t="n">
         <v>3.3</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.62</v>
       </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '79']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '90']</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.67</v>
+        <v>3.8</v>
       </c>
       <c r="M18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.5</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T18" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['12', '48']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.625</v>
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="M19" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.44</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2987,32 +2987,32 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.13</v>
+        <v>5.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
         <v>3.4</v>
@@ -3021,47 +3021,47 @@
         <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB20" t="n">
         <v>1.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '89']</t>
         </is>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" t="n">
         <v>1.44</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.73</v>
       </c>
       <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.44</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         <v>1.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ22" t="n">
         <v>3.75</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -628,127 +628,127 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>['34', '63', '71']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45890.41666666666</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,91 +901,91 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N4" t="n">
-        <v>18</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X4" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['34', '63', '71']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.28</v>
+        <v>1.73</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45890.45833333334</v>
+        <v>45890.5</v>
       </c>
     </row>
     <row r="5">
@@ -1020,26 +1020,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.97</v>
+        <v>2.37</v>
       </c>
       <c r="M5" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="N5" t="n">
-        <v>3.69</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.4</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45890.5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.2</v>
+        <v>2.08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2.25</v>
       </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Z7" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['11', '84', '89']</t>
+          <t>['82', '90+10']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>5.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.96</v>
+        <v>2.99</v>
       </c>
       <c r="N9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="O9" t="n">
+      <c r="U9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X9" t="n">
         <v>2.25</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.15</v>
       </c>
-      <c r="X9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['82', '90+10']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.31</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
-        <v>9.25</v>
+        <v>2.29</v>
       </c>
       <c r="P10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['11', '84', '89']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2.05</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['23', '26', '45+4', '48']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AI10" t="n">
-        <v>4.3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.37</v>
+        <v>2.55</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>1.31</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>9.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.13</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '26', '45+4', '48']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['57', '90']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.1</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>6.69</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="AA17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['57', '90']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="M18" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.44</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['12', '48']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.625</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.67</v>
+        <v>3.8</v>
       </c>
       <c r="M19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['12', '48']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
@@ -3103,20 +3103,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '60']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3223,106 +3223,106 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG22" t="n">
         <v>1.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ22" t="n">
         <v>3.75</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3374,65 +3374,65 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.75</v>
@@ -3490,20 +3490,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3516,13 +3516,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
         <v>1.2</v>
@@ -3534,25 +3534,25 @@
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
         <v>5.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
         <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB24" t="n">
         <v>1.68</v>
@@ -3561,23 +3561,23 @@
         <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '15', '29']</t>
         </is>
       </c>
       <c r="AG24" t="n">
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -3632,81 +3632,81 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="N25" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8</v>
+        <v>4.26</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
         <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>

--- a/jogos_2025-08-21.xlsx
+++ b/jogos_2025-08-21.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,26 +891,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -923,69 +923,69 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45890.5</v>
@@ -1149,26 +1149,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1181,87 +1181,87 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45890.5</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X7" t="n">
         <v>3.14</v>
       </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Y7" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z7" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '84', '89']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>1.69</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>9.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
         <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1635,20 +1635,20 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '26', '45+4', '48']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['11', '84', '89']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1804,88 +1804,88 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>9</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="O11" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
         <v>1.65</v>
       </c>
       <c r="X11" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.42</v>
       </c>
-      <c r="AA11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['23', '26', '45+4', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45890.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45890.52083333334</v>
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA16" t="n">
         <v>3.3</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['55', '79']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.62</v>
       </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['55', '79']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45890.60416666666</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.67</v>
+        <v>3.8</v>
       </c>
       <c r="M18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.5</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T18" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['12', '48']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45890.625</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="M19" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.44</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['12', '48']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45890.625</v>
